--- a/outputs/230-16.xlsx
+++ b/outputs/230-16.xlsx
@@ -21,17 +21,50 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+  <si>
+    <t xml:space="preserve">Sub SplitSubstrings()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Dim r As Long, p As Long, t As String</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    For r = 1 To Cells(Rows.Count, 1).End(xlUp).Row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        t = Cells(r, 1).Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        If Len(t) Then</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            For p = 1 To Len(t): If Mid(t, p, 1) Like "[a-zA-Z]" Then Exit For: Next p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            If p &lt;= Len(t) Then Cells(r, 2) = Mid(t, p): Cells(r, 1) = Left(t, p - 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        End If</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Next r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End Sub</t>
+  </si>
   <si>
     <t xml:space="preserve">data</t>
   </si>
   <si>
-    <t xml:space="preserve">string1</t>
-  </si>
-  <si>
     <t xml:space="preserve">2020-02-21 09:58:34.595555</t>
   </si>
   <si>
+    <t xml:space="preserve">event_type="BUSINESS"</t>
+  </si>
+  <si>
     <t xml:space="preserve">2020-02-22 14:35:59.356666</t>
   </si>
   <si>
@@ -51,9 +84,6 @@
   </si>
   <si>
     <t xml:space="preserve">2020-02-23 14:40:10.431 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">event_type="BUSINESS"</t>
   </si>
 </sst>
 </file>
@@ -130,16 +160,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -335,87 +369,89 @@
   <dimension ref="A1:B19"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="127.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="127.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.89"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1"/>
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1"/>
+      <c r="A11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1"/>
+      <c r="A12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1"/>
+      <c r="A13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
+      <c r="A14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
+      <c r="A15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
+      <c r="A16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
+      <c r="A17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
+      <c r="A18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
+      <c r="A19" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -436,80 +472,80 @@
   <dimension ref="A2:B10"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.89"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="0" t="s">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>10</v>
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>10</v>
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>10</v>
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>10</v>
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>10</v>
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>10</v>
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>10</v>
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>10</v>
+      <c r="A10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/230-16.xlsx
+++ b/outputs/230-16.xlsx
@@ -21,42 +21,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
-  <si>
-    <t xml:space="preserve">Sub SplitSubstrings()</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
+  <si>
+    <t xml:space="preserve">data</t>
   </si>
   <si>
     <t xml:space="preserve">string1</t>
   </si>
   <si>
-    <t xml:space="preserve">    Dim r As Long, p As Long, t As String</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    For r = 1 To Cells(Rows.Count, 1).End(xlUp).Row</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        t = Cells(r, 1).Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        If Len(t) Then</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            For p = 1 To Len(t): If Mid(t, p, 1) Like "[a-zA-Z]" Then Exit For: Next p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            If p &lt;= Len(t) Then Cells(r, 2) = Mid(t, p): Cells(r, 1) = Left(t, p - 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        End If</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Next r</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End Sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data</t>
+    <t xml:space="preserve">2020-02-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:58:34.595555 event_type="BUSINESS"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-02-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:35:59.356666 event_type="BUSINESS"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-02-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:41:01.412 event_type="BUSINESS"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:40:11.618 event_type="BUSINESS"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:40:11.184 event_type="BUSINESS"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:40:11.141 event_type="BUSINESS"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:40:10.997 event_type="BUSINESS"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:40:10.431 event_type="BUSINESS"</t>
   </si>
   <si>
     <t xml:space="preserve">2020-02-21 09:58:34.595555</t>
@@ -385,46 +388,68 @@
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="A10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
@@ -478,7 +503,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -486,66 +511,66 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
